--- a/www/flightdata/xlsx/eoss-384.xlsx
+++ b/www/flightdata/xlsx/eoss-384.xlsx
@@ -2820,7 +2820,7 @@
         <v>31019.5</v>
       </c>
       <c r="I2">
-        <v>599</v>
+        <v>333</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
